--- a/DOCS/MeasurementAnalysis-Tester-nr-001.xlsx
+++ b/DOCS/MeasurementAnalysis-Tester-nr-001.xlsx
@@ -321,16 +321,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="General"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
-    <numFmt numFmtId="168" formatCode="0.000E+00"/>
-    <numFmt numFmtId="169" formatCode="0.0"/>
-    <numFmt numFmtId="170" formatCode="0.00"/>
-    <numFmt numFmtId="171" formatCode="0.00%"/>
-    <numFmt numFmtId="172" formatCode="0"/>
+    <numFmt numFmtId="168" formatCode="0.000000"/>
+    <numFmt numFmtId="169" formatCode="0.000E+00"/>
+    <numFmt numFmtId="170" formatCode="0.0"/>
+    <numFmt numFmtId="171" formatCode="0.00"/>
+    <numFmt numFmtId="172" formatCode="0.00%"/>
+    <numFmt numFmtId="173" formatCode="0"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -547,10 +548,6 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -559,7 +556,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -587,7 +584,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -603,19 +604,19 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="172" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -623,7 +624,7 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -631,11 +632,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -655,15 +656,15 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -857,8 +858,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="37.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="36.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="53.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="29.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="53.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="29.49"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="79.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -883,175 +884,178 @@
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
-      <c r="E2" s="6"/>
+      <c r="E2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="8" t="n">
+      <c r="B3" s="7" t="n">
         <v>99.456</v>
       </c>
-      <c r="C3" s="8" t="n">
+      <c r="C3" s="7" t="n">
         <v>198.036</v>
       </c>
       <c r="D3" s="5" t="n">
         <v>999.466</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10"/>
-      <c r="B4" s="8" t="n">
+      <c r="A4" s="9"/>
+      <c r="B4" s="7" t="n">
         <v>99.42</v>
       </c>
-      <c r="C4" s="8" t="n">
+      <c r="C4" s="7" t="n">
         <v>197.972</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>999.452</v>
       </c>
-      <c r="E4" s="9"/>
+      <c r="E4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10"/>
-      <c r="B5" s="8" t="n">
+      <c r="A5" s="9"/>
+      <c r="B5" s="7" t="n">
         <v>99.45</v>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="7" t="n">
         <v>197.996</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>999.475</v>
       </c>
-      <c r="E5" s="9"/>
+      <c r="E5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10"/>
-      <c r="B6" s="8" t="n">
+      <c r="A6" s="9"/>
+      <c r="B6" s="7" t="n">
         <v>99.474</v>
       </c>
-      <c r="C6" s="8" t="n">
+      <c r="C6" s="7" t="n">
         <v>197.988</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>999.403</v>
       </c>
-      <c r="E6" s="9"/>
+      <c r="E6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10"/>
-      <c r="B7" s="8" t="n">
+      <c r="A7" s="9"/>
+      <c r="B7" s="7" t="n">
         <v>99.449</v>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="7" t="n">
         <v>197.972</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>999.515</v>
       </c>
-      <c r="E7" s="9"/>
+      <c r="E7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10"/>
-      <c r="B8" s="8" t="n">
+      <c r="A8" s="9"/>
+      <c r="B8" s="7" t="n">
         <v>99.475</v>
       </c>
-      <c r="C8" s="8" t="n">
+      <c r="C8" s="7" t="n">
         <v>197.996</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>999.514</v>
       </c>
-      <c r="E8" s="9"/>
+      <c r="E8" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="10" t="n">
         <f aca="false">AVERAGE(B3:B8)</f>
         <v>99.454</v>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="C9" s="11" t="n">
         <f aca="false">AVERAGE(C3:C8)</f>
         <v>197.993333333333</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="D9" s="11" t="n">
         <f aca="false">AVERAGE(D3:D8)</f>
         <v>999.470833333333</v>
       </c>
-      <c r="E9" s="9"/>
+      <c r="E9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="13" t="n">
+      <c r="B10" s="12" t="n">
         <f aca="false">STDEV(B3:B8)</f>
         <v>0.0202089089265096</v>
       </c>
-      <c r="C10" s="13" t="n">
+      <c r="C10" s="12" t="n">
         <f aca="false">STDEV(C3:C8)</f>
         <v>0.0235513623102055</v>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="12" t="n">
         <f aca="false">STDEV(D3:D8)</f>
         <v>0.0419781689294101</v>
       </c>
-      <c r="E10" s="9"/>
+      <c r="E10" s="8"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="13" t="n">
+      <c r="B11" s="12" t="n">
         <f aca="false">B10/SQRT(6)</f>
         <v>0.00825025252138746</v>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="12" t="n">
         <f aca="false">C10/SQRT(6)</f>
         <v>0.00961480340123644</v>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="12" t="n">
         <f aca="false">D10/SQRT(6)</f>
         <v>0.0171375157022349</v>
       </c>
-      <c r="E11" s="9"/>
+      <c r="E11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="9"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="8"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="13" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>0.0024</v>
+        <f aca="false">0.0024/2</f>
+        <v>0.0012</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.0024</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="E13" s="9"/>
+        <f aca="false">0.0024/2</f>
+        <v>0.0012</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <f aca="false">0.00003/2</f>
+        <v>1.5E-005</v>
+      </c>
+      <c r="E13" s="8"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10"/>
+      <c r="A14" s="9"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
-      <c r="E14" s="9"/>
+      <c r="E14" s="8"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B15" s="5" t="n">
@@ -1063,10 +1067,10 @@
       <c r="D15" s="5" t="n">
         <v>1E-005</v>
       </c>
-      <c r="E15" s="9"/>
+      <c r="E15" s="8"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B16" s="15" t="n">
@@ -1081,60 +1085,60 @@
         <f aca="false">D15/SQRT(12)</f>
         <v>2.88675134594813E-006</v>
       </c>
-      <c r="E16" s="9"/>
+      <c r="E16" s="8"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10"/>
+      <c r="A17" s="9"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
-      <c r="E17" s="9"/>
+      <c r="E17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="8" t="n">
+      <c r="B18" s="7" t="n">
         <f aca="false">SQRT(B11^2+B13^2+B16^2)</f>
-        <v>0.00859224505004329</v>
-      </c>
-      <c r="C18" s="8" t="n">
+        <v>0.00833706633055018</v>
+      </c>
+      <c r="C18" s="7" t="n">
         <f aca="false">SQRT(C11^2+C13^2+C16^2)</f>
-        <v>0.00990981598102413</v>
-      </c>
-      <c r="D18" s="8" t="n">
+        <v>0.00968939898950194</v>
+      </c>
+      <c r="D18" s="7" t="n">
         <f aca="false">SQRT(D11^2+D13^2+D16^2)</f>
-        <v>0.0294905824421574</v>
-      </c>
-      <c r="E18" s="9"/>
+        <v>0.0171375225099103</v>
+      </c>
+      <c r="E18" s="8"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="8" t="n">
+      <c r="B19" s="7" t="n">
         <f aca="false">B18*2</f>
-        <v>0.0171844901000866</v>
-      </c>
-      <c r="C19" s="8" t="n">
+        <v>0.0166741326611004</v>
+      </c>
+      <c r="C19" s="7" t="n">
         <f aca="false">C18*2</f>
-        <v>0.0198196319620483</v>
-      </c>
-      <c r="D19" s="8" t="n">
+        <v>0.0193787979790039</v>
+      </c>
+      <c r="D19" s="7" t="n">
         <f aca="false">D18*2</f>
-        <v>0.0589811648843148</v>
-      </c>
-      <c r="E19" s="9"/>
+        <v>0.0342750450198205</v>
+      </c>
+      <c r="E19" s="8"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10"/>
+      <c r="A20" s="9"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
-      <c r="E20" s="9"/>
+      <c r="E20" s="8"/>
     </row>
     <row r="21" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="6" t="s">
         <v>15</v>
       </c>
       <c r="B21" s="16" t="str">
@@ -1143,13 +1147,13 @@
       </c>
       <c r="C21" s="16" t="str">
         <f aca="false">"( " &amp; TEXT(C9,"0,000") &amp; "  ± " &amp; TEXT(C19,"0,000") &amp; " )"  &amp; " MΩ"</f>
-        <v>( 197,993  ± 0,020 ) MΩ</v>
+        <v>( 197,993  ± 0,019 ) MΩ</v>
       </c>
       <c r="D21" s="16" t="str">
         <f aca="false">"( " &amp; TEXT(D9,"0,000") &amp; "  ± " &amp; TEXT(D19,"0,000") &amp; " )"  &amp; " MΩ"</f>
-        <v>( 999,471  ± 0,059 ) MΩ</v>
-      </c>
-      <c r="E21" s="9"/>
+        <v>( 999,471  ± 0,034 ) MΩ</v>
+      </c>
+      <c r="E21" s="8"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="17"/>
@@ -1185,18 +1189,18 @@
       <c r="F27" s="20"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="6" t="s">
         <v>21</v>
       </c>
       <c r="B28" s="5" t="n">
         <f aca="false">B9</f>
         <v>99.454</v>
       </c>
-      <c r="C28" s="8" t="n">
+      <c r="C28" s="7" t="n">
         <f aca="false">C9</f>
         <v>197.993333333333</v>
       </c>
-      <c r="D28" s="8" t="n">
+      <c r="D28" s="7" t="n">
         <f aca="false">D9</f>
         <v>999.470833333333</v>
       </c>
@@ -1204,26 +1208,26 @@
       <c r="F28" s="20"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B29" s="8" t="n">
+      <c r="B29" s="7" t="n">
         <f aca="false">B18</f>
-        <v>0.00859224505004329</v>
-      </c>
-      <c r="C29" s="8" t="n">
+        <v>0.00833706633055018</v>
+      </c>
+      <c r="C29" s="7" t="n">
         <f aca="false">C18</f>
-        <v>0.00990981598102413</v>
-      </c>
-      <c r="D29" s="8" t="n">
+        <v>0.00968939898950194</v>
+      </c>
+      <c r="D29" s="7" t="n">
         <f aca="false">D18</f>
-        <v>0.0294905824421574</v>
+        <v>0.0171375225099103</v>
       </c>
       <c r="E29" s="20"/>
       <c r="F29" s="20"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="10"/>
+      <c r="A30" s="9"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
@@ -1231,14 +1235,14 @@
       <c r="F30" s="20"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B31" s="11" t="n">
+      <c r="B31" s="10" t="n">
         <f aca="false">AVERAGE(B66:B71)</f>
         <v>98.385</v>
       </c>
-      <c r="C31" s="11" t="n">
+      <c r="C31" s="10" t="n">
         <f aca="false">AVERAGE(C66:C71)</f>
         <v>196.25</v>
       </c>
@@ -1252,18 +1256,18 @@
       <c r="F31" s="22"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="14" t="s">
+      <c r="A32" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B32" s="8" t="n">
+      <c r="B32" s="7" t="n">
         <f aca="false">B28-B31</f>
         <v>1.069</v>
       </c>
-      <c r="C32" s="8" t="n">
+      <c r="C32" s="7" t="n">
         <f aca="false">C28-C31</f>
         <v>1.743333333333</v>
       </c>
-      <c r="D32" s="8" t="n">
+      <c r="D32" s="7" t="n">
         <f aca="false">D28-D31</f>
         <v>13.2874999999996</v>
       </c>
@@ -1271,7 +1275,7 @@
       <c r="F32" s="22"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="14" t="s">
+      <c r="A33" s="13" t="s">
         <v>25</v>
       </c>
       <c r="B33" s="23" t="n">
@@ -1290,18 +1294,18 @@
       <c r="F33" s="22"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B34" s="13" t="n">
+      <c r="B34" s="12" t="n">
         <f aca="false">STDEV(B66:B71)</f>
         <v>0.0327108544675929</v>
       </c>
-      <c r="C34" s="13" t="n">
+      <c r="C34" s="12" t="n">
         <f aca="false">STDEV(C66:C71)</f>
         <v>0.0547722557505291</v>
       </c>
-      <c r="D34" s="13" t="n">
+      <c r="D34" s="12" t="n">
         <f aca="false">STDEV(D66:D71)</f>
         <v>0.788458411501005</v>
       </c>
@@ -1309,18 +1313,18 @@
       <c r="F34" s="22"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B35" s="13" t="n">
+      <c r="B35" s="12" t="n">
         <f aca="false">B34/SQRT(6)</f>
         <v>0.013354150416007</v>
       </c>
-      <c r="C35" s="13" t="n">
+      <c r="C35" s="12" t="n">
         <f aca="false">C34/SQRT(6)</f>
         <v>0.022360679775003</v>
       </c>
-      <c r="D35" s="13" t="n">
+      <c r="D35" s="12" t="n">
         <f aca="false">D34/SQRT(6)</f>
         <v>0.321886798597139</v>
       </c>
@@ -1328,7 +1332,7 @@
       <c r="F35" s="22"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="10"/>
+      <c r="A36" s="9"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
@@ -1336,7 +1340,7 @@
       <c r="F36" s="22"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="6" t="s">
         <v>11</v>
       </c>
       <c r="B37" s="5" t="n">
@@ -1355,7 +1359,7 @@
       <c r="F37" s="22"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="6" t="s">
         <v>12</v>
       </c>
       <c r="B38" s="15" t="n">
@@ -1374,7 +1378,7 @@
       <c r="F38" s="22"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="10"/>
+      <c r="A39" s="9"/>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
@@ -1382,53 +1386,53 @@
       <c r="F39" s="22"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B40" s="8" t="n">
+      <c r="B40" s="7" t="n">
         <f aca="false">SQRT(B29^2+B35^2+B38^2)</f>
-        <v>0.0161398061223383</v>
-      </c>
-      <c r="C40" s="8" t="n">
+        <v>0.0160054160104218</v>
+      </c>
+      <c r="C40" s="7" t="n">
         <f aca="false">SQRT(C29^2+C35^2+C38^2)</f>
-        <v>0.0378356681731844</v>
-      </c>
-      <c r="D40" s="8" t="n">
+        <v>0.0377785360503994</v>
+      </c>
+      <c r="D40" s="7" t="n">
         <f aca="false">SQRT(D29^2+D35^2+D38^2)</f>
-        <v>0.324521399752352</v>
+        <v>0.32363272257642</v>
       </c>
       <c r="E40" s="22"/>
       <c r="F40" s="22"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="7" t="s">
+      <c r="A41" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B41" s="8" t="n">
+      <c r="B41" s="7" t="n">
         <f aca="false">B40*2</f>
-        <v>0.0322796122446765</v>
-      </c>
-      <c r="C41" s="8" t="n">
+        <v>0.0320108320208436</v>
+      </c>
+      <c r="C41" s="7" t="n">
         <f aca="false">C40*2</f>
-        <v>0.0756713363463689</v>
-      </c>
-      <c r="D41" s="8" t="n">
+        <v>0.0755570721007987</v>
+      </c>
+      <c r="D41" s="7" t="n">
         <f aca="false">D40*2</f>
-        <v>0.649042799504704</v>
+        <v>0.64726544515284</v>
       </c>
       <c r="E41" s="22"/>
       <c r="F41" s="22"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="7"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
+      <c r="A42" s="6"/>
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
       <c r="E42" s="22"/>
       <c r="F42" s="22"/>
     </row>
     <row r="43" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="7" t="s">
+      <c r="A43" s="6" t="s">
         <v>15</v>
       </c>
       <c r="B43" s="16" t="str">
@@ -1441,13 +1445,13 @@
       </c>
       <c r="D43" s="16" t="str">
         <f aca="false">"( " &amp; TEXT(D31,"0,000") &amp; "  ± " &amp; TEXT(D41,"0,000") &amp; " )"  &amp; " MΩ"</f>
-        <v>( 986,183  ± 0,649 ) MΩ</v>
+        <v>( 986,183  ± 0,647 ) MΩ</v>
       </c>
       <c r="E43" s="22"/>
       <c r="F43" s="22"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="10"/>
+      <c r="A44" s="9"/>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
